--- a/artfynd/A 36958-2023 artfynd.xlsx
+++ b/artfynd/A 36958-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 36958-2023 artfynd.xlsx
+++ b/artfynd/A 36958-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY118"/>
+  <dimension ref="A1:AY122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>372677</v>
+        <v>112013852</v>
       </c>
       <c r="B2" t="n">
-        <v>89406</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91859</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1204</v>
+        <v>112</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +710,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>537676.2012955723</v>
+        <v>537929</v>
       </c>
       <c r="R2" t="n">
-        <v>7191324.05986992</v>
+        <v>7191147</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +740,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2012-08-26</t>
+          <t>2023-09-10</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2012-08-26</t>
+          <t>2023-09-10</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -771,36 +766,26 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>SCA Naturvärdesinventeringar</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Via SCA Naturvärdesinventeringar</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>372681</v>
+        <v>112013853</v>
       </c>
       <c r="B3" t="n">
-        <v>89406</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91859</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -808,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1204</v>
+        <v>112</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -832,13 +817,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>538047.9156609075</v>
+        <v>537930</v>
       </c>
       <c r="R3" t="n">
-        <v>7191347.048829023</v>
+        <v>7191154</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -862,22 +847,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2012-08-26</t>
+          <t>2023-09-10</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2012-08-26</t>
+          <t>2023-09-10</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -888,36 +873,26 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>SCA Naturvärdesinventeringar</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Via SCA Naturvärdesinventeringar</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>372680</v>
+        <v>112013955</v>
       </c>
       <c r="B4" t="n">
-        <v>89406</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89292</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -925,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1204</v>
+        <v>510</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -949,13 +924,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>537763.8649565168</v>
+        <v>537931</v>
       </c>
       <c r="R4" t="n">
-        <v>7191028.500333085</v>
+        <v>7191155</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -979,22 +954,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2012-08-26</t>
+          <t>2023-09-10</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2012-08-26</t>
+          <t>2023-09-10</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1005,36 +980,26 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>SCA Naturvärdesinventeringar</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Via SCA Naturvärdesinventeringar</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>901007</v>
+        <v>112013879</v>
       </c>
       <c r="B5" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1042,21 +1007,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2081</v>
+        <v>658</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1066,13 +1031,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>537968.6348413597</v>
+        <v>537709</v>
       </c>
       <c r="R5" t="n">
-        <v>7191449.890281525</v>
+        <v>7191221</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1096,22 +1061,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2012-08-26</t>
+          <t>2023-09-10</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2012-08-26</t>
+          <t>2023-09-10</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1122,36 +1087,26 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>SCA Naturvärdesinventeringar</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Via SCA Naturvärdesinventeringar</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>901006</v>
+        <v>112013899</v>
       </c>
       <c r="B6" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1159,21 +1114,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2081</v>
+        <v>864</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1183,13 +1138,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>538047.9156609075</v>
+        <v>537696</v>
       </c>
       <c r="R6" t="n">
-        <v>7191347.048829023</v>
+        <v>7191136</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1213,22 +1168,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2012-08-26</t>
+          <t>2023-09-10</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2012-08-26</t>
+          <t>2023-09-10</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1239,36 +1194,26 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>SCA Naturvärdesinventeringar</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Via SCA Naturvärdesinventeringar</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>1994518</v>
+        <v>112013900</v>
       </c>
       <c r="B7" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1276,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>864</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1300,13 +1245,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>538047.9156609075</v>
+        <v>537918</v>
       </c>
       <c r="R7" t="n">
-        <v>7191347.048829023</v>
+        <v>7191139</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1330,22 +1275,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2012-08-26</t>
+          <t>2023-09-10</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2012-08-26</t>
+          <t>2023-09-10</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1356,36 +1301,26 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>SCA Naturvärdesinventeringar</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Via SCA Naturvärdesinventeringar</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>372682</v>
+        <v>112013901</v>
       </c>
       <c r="B8" t="n">
-        <v>89406</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1393,21 +1328,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1204</v>
+        <v>1108</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1417,13 +1352,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>538019.7375235006</v>
+        <v>537719</v>
       </c>
       <c r="R8" t="n">
-        <v>7191418.617803372</v>
+        <v>7191055</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1447,22 +1382,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2012-08-26</t>
+          <t>2023-09-10</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2012-08-26</t>
+          <t>2023-09-10</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1473,36 +1408,26 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>SCA Naturvärdesinventeringar</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Via SCA Naturvärdesinventeringar</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>103301877</v>
+        <v>112013902</v>
       </c>
       <c r="B9" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1510,40 +1435,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1312</v>
+        <v>1108</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Ryptjärnberg, Ås lm</t>
+          <t>Ryptjärnberget, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>538086.5361383723</v>
+        <v>538111</v>
       </c>
       <c r="R9" t="n">
-        <v>7191292.209691478</v>
+        <v>7191368</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1567,22 +1489,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2022-09-01</t>
+          <t>2023-09-10</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2022-09-01</t>
+          <t>2023-09-10</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1591,56 +1513,50 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Nils Åslund</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Nils Åslund</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>112013833</v>
+        <v>372677</v>
       </c>
       <c r="B10" t="n">
-        <v>73835</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6440</v>
+        <v>1204</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1650,13 +1566,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>537972</v>
+        <v>537676</v>
       </c>
       <c r="R10" t="n">
-        <v>7191315</v>
+        <v>7191324</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1680,22 +1596,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2023-09-10</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>10:36</t>
+          <t>2012-08-26</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2023-09-10</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>10:36</t>
+          <t>2012-08-26</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1706,35 +1612,35 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>SCA Naturvärdesinventeringar</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Via SCA Naturvärdesinventeringar</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>112013909</v>
+        <v>372680</v>
       </c>
       <c r="B11" t="n">
-        <v>89568</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1765,10 +1671,10 @@
         <v>537764</v>
       </c>
       <c r="R11" t="n">
-        <v>7191026</v>
+        <v>7191029</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1792,22 +1698,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2023-09-10</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>11:47</t>
+          <t>2012-08-26</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2023-09-10</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>11:47</t>
+          <t>2012-08-26</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1818,53 +1714,53 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>SCA Naturvärdesinventeringar</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Via SCA Naturvärdesinventeringar</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>112013925</v>
+        <v>372681</v>
       </c>
       <c r="B12" t="n">
-        <v>77651</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1874,13 +1770,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>537657</v>
+        <v>538048</v>
       </c>
       <c r="R12" t="n">
-        <v>7191464</v>
+        <v>7191347</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1904,22 +1800,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2023-09-10</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>12:25</t>
+          <t>2012-08-26</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2023-09-10</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>12:25</t>
+          <t>2012-08-26</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1930,53 +1816,53 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>SCA Naturvärdesinventeringar</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Via SCA Naturvärdesinventeringar</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>112013920</v>
+        <v>372682</v>
       </c>
       <c r="B13" t="n">
-        <v>77651</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1986,13 +1872,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>537932</v>
+        <v>538020</v>
       </c>
       <c r="R13" t="n">
-        <v>7191471</v>
+        <v>7191419</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2016,22 +1902,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2023-09-10</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>13:42</t>
+          <t>2012-08-26</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2023-09-10</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>13:42</t>
+          <t>2012-08-26</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2042,48 +1918,53 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>SCA Naturvärdesinventeringar</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Via SCA Naturvärdesinventeringar</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>112013897</v>
+        <v>112013905</v>
       </c>
       <c r="B14" t="n">
-        <v>89939</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6040186</v>
+        <v>1204</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Gränsticka</t>
+        </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2093,10 +1974,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>537926</v>
+        <v>537884</v>
       </c>
       <c r="R14" t="n">
-        <v>7191144</v>
+        <v>7191449</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2128,7 +2009,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2138,7 +2019,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2165,37 +2046,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>112013891</v>
+        <v>112013906</v>
       </c>
       <c r="B15" t="n">
-        <v>78748</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6464</v>
+        <v>1204</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2205,10 +2081,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>538029</v>
+        <v>537811</v>
       </c>
       <c r="R15" t="n">
-        <v>7191489</v>
+        <v>7191479</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2240,7 +2116,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2250,7 +2126,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2277,37 +2153,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>112013916</v>
+        <v>112013907</v>
       </c>
       <c r="B16" t="n">
-        <v>77651</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2317,10 +2188,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>538029</v>
+        <v>537753</v>
       </c>
       <c r="R16" t="n">
-        <v>7191492</v>
+        <v>7191465</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2352,7 +2223,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2362,7 +2233,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2389,37 +2260,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>112013856</v>
+        <v>112013908</v>
       </c>
       <c r="B17" t="n">
-        <v>78715</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2081</v>
+        <v>1204</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2429,10 +2295,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>538029</v>
+        <v>537709</v>
       </c>
       <c r="R17" t="n">
-        <v>7191489</v>
+        <v>7191221</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2464,7 +2330,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2474,7 +2340,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2501,19 +2367,14 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>112013912</v>
+        <v>112013909</v>
       </c>
       <c r="B18" t="n">
-        <v>89568</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -2541,10 +2402,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>538050</v>
+        <v>537764</v>
       </c>
       <c r="R18" t="n">
-        <v>7191345</v>
+        <v>7191027</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2576,7 +2437,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2586,7 +2447,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2613,37 +2474,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>112013872</v>
+        <v>112013910</v>
       </c>
       <c r="B19" t="n">
-        <v>78715</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2081</v>
+        <v>1204</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2653,10 +2509,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>538123</v>
+        <v>537930</v>
       </c>
       <c r="R19" t="n">
-        <v>7191380</v>
+        <v>7191312</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2688,7 +2544,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2698,7 +2554,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2725,37 +2581,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>112013875</v>
+        <v>112013911</v>
       </c>
       <c r="B20" t="n">
-        <v>78715</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2081</v>
+        <v>1204</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2765,10 +2616,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>538139</v>
+        <v>538047</v>
       </c>
       <c r="R20" t="n">
-        <v>7191426</v>
+        <v>7191331</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2800,7 +2651,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2810,7 +2661,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2837,37 +2688,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>112013868</v>
+        <v>112013912</v>
       </c>
       <c r="B21" t="n">
-        <v>78715</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2081</v>
+        <v>1204</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2877,10 +2723,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>538057</v>
+        <v>538050</v>
       </c>
       <c r="R21" t="n">
-        <v>7191362</v>
+        <v>7191345</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2912,7 +2758,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2922,7 +2768,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2949,19 +2795,14 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>112013905</v>
+        <v>112013913</v>
       </c>
       <c r="B22" t="n">
-        <v>89568</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
@@ -2989,10 +2830,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>537883</v>
+        <v>538066</v>
       </c>
       <c r="R22" t="n">
-        <v>7191449</v>
+        <v>7191378</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3024,7 +2865,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3034,7 +2875,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3061,15 +2902,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>112013838</v>
+        <v>103301877</v>
       </c>
       <c r="B23" t="n">
-        <v>78217</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3077,37 +2913,40 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>229821</v>
+        <v>1312</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Ryptjärnberget, Ås lm</t>
+          <t>Ryptjärnberg, Ås lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>537889</v>
+        <v>538087</v>
       </c>
       <c r="R23" t="n">
-        <v>7191123</v>
+        <v>7191292</v>
       </c>
       <c r="S23" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3131,22 +2970,22 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2023-09-10</t>
+          <t>2022-09-01</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2023-09-10</t>
+          <t>2022-09-01</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3155,33 +2994,29 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Nils Åslund</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Nils Åslund</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>112013923</v>
+        <v>112013954</v>
       </c>
       <c r="B24" t="n">
-        <v>77651</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3189,21 +3024,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3213,10 +3048,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>537799</v>
+        <v>537931</v>
       </c>
       <c r="R24" t="n">
-        <v>7191449</v>
+        <v>7191310</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3248,7 +3083,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3258,7 +3093,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3285,37 +3120,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>112013830</v>
+        <v>901006</v>
       </c>
       <c r="B25" t="n">
-        <v>103779</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221725</v>
+        <v>2081</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3325,13 +3155,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>538171</v>
+        <v>538048</v>
       </c>
       <c r="R25" t="n">
-        <v>7191412</v>
+        <v>7191347</v>
       </c>
       <c r="S25" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3355,22 +3185,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2023-09-10</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>09:43</t>
+          <t>2012-08-26</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2023-09-10</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>09:43</t>
+          <t>2012-08-26</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3381,31 +3201,31 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>SCA Naturvärdesinventeringar</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Via SCA Naturvärdesinventeringar</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>112013862</v>
+        <v>901007</v>
       </c>
       <c r="B26" t="n">
-        <v>78715</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3437,13 +3257,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>537620</v>
+        <v>537969</v>
       </c>
       <c r="R26" t="n">
-        <v>7191360</v>
+        <v>7191450</v>
       </c>
       <c r="S26" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3467,22 +3287,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2023-09-10</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>12:10</t>
+          <t>2012-08-26</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2023-09-10</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>12:10</t>
+          <t>2012-08-26</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3493,53 +3303,53 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>SCA Naturvärdesinventeringar</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Via SCA Naturvärdesinventeringar</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>112013847</v>
+        <v>112013856</v>
       </c>
       <c r="B27" t="n">
-        <v>78741</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3549,10 +3359,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>538057</v>
+        <v>538029</v>
       </c>
       <c r="R27" t="n">
-        <v>7191362</v>
+        <v>7191489</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3584,7 +3394,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3594,7 +3404,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3621,15 +3431,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>112013929</v>
+        <v>112013857</v>
       </c>
       <c r="B28" t="n">
-        <v>77651</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3637,21 +3442,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3661,10 +3466,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>537696</v>
+        <v>537998</v>
       </c>
       <c r="R28" t="n">
-        <v>7191132</v>
+        <v>7191490</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3696,7 +3501,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3706,7 +3511,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3733,37 +3538,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>112013839</v>
+        <v>112013859</v>
       </c>
       <c r="B29" t="n">
-        <v>90236</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>3298</v>
+        <v>2081</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3773,10 +3573,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>537982</v>
+        <v>537984</v>
       </c>
       <c r="R29" t="n">
-        <v>7191483</v>
+        <v>7191480</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3808,7 +3608,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3818,7 +3618,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3845,15 +3645,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>112013921</v>
+        <v>112013860</v>
       </c>
       <c r="B30" t="n">
-        <v>77651</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3861,21 +3656,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3885,10 +3680,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>537877</v>
+        <v>537969</v>
       </c>
       <c r="R30" t="n">
-        <v>7191453</v>
+        <v>7191507</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3920,7 +3715,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3930,7 +3725,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3957,37 +3752,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>112013895</v>
+        <v>112013861</v>
       </c>
       <c r="B31" t="n">
-        <v>78748</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6464</v>
+        <v>2081</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3997,10 +3787,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>538123</v>
+        <v>537931</v>
       </c>
       <c r="R31" t="n">
-        <v>7191387</v>
+        <v>7191474</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4032,7 +3822,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4042,7 +3832,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4069,15 +3859,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>112013935</v>
+        <v>112013862</v>
       </c>
       <c r="B32" t="n">
-        <v>77651</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4085,21 +3870,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4109,10 +3894,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>537926</v>
+        <v>537620</v>
       </c>
       <c r="R32" t="n">
-        <v>7191143</v>
+        <v>7191361</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4144,7 +3929,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4154,7 +3939,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4181,15 +3966,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>112013937</v>
+        <v>112013863</v>
       </c>
       <c r="B33" t="n">
-        <v>77651</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4197,21 +3977,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4221,10 +4001,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>537929</v>
+        <v>537967</v>
       </c>
       <c r="R33" t="n">
-        <v>7191154</v>
+        <v>7191330</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4256,7 +4036,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4266,7 +4046,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4293,15 +4073,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>112013881</v>
+        <v>112013865</v>
       </c>
       <c r="B34" t="n">
-        <v>78714</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4309,21 +4084,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4333,10 +4108,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>538024</v>
+        <v>538033</v>
       </c>
       <c r="R34" t="n">
-        <v>7191282</v>
+        <v>7191291</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4368,7 +4143,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4378,7 +4153,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4405,15 +4180,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>112013898</v>
+        <v>112013866</v>
       </c>
       <c r="B35" t="n">
-        <v>56577</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4421,38 +4191,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>103022</v>
+        <v>2081</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lappmes</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Poecile cinctus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Boddaert, 1783)</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Ryptjärnberget, Ås lm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>537891</v>
+        <v>538055</v>
       </c>
       <c r="R35" t="n">
-        <v>7191464</v>
+        <v>7191309</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4484,7 +4250,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4494,7 +4260,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4521,15 +4287,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>112013953</v>
+        <v>112013867</v>
       </c>
       <c r="B36" t="n">
-        <v>77651</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4537,21 +4298,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4561,10 +4322,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>538198</v>
+        <v>538051</v>
       </c>
       <c r="R36" t="n">
-        <v>7191468</v>
+        <v>7191344</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4596,7 +4357,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4606,7 +4367,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4633,15 +4394,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>112013884</v>
+        <v>112013868</v>
       </c>
       <c r="B37" t="n">
-        <v>78714</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4649,21 +4405,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4673,10 +4429,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>538048</v>
+        <v>538057</v>
       </c>
       <c r="R37" t="n">
-        <v>7191309</v>
+        <v>7191362</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4708,7 +4464,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4718,7 +4474,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4745,37 +4501,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>112013850</v>
+        <v>112013869</v>
       </c>
       <c r="B38" t="n">
-        <v>78741</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4785,10 +4536,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>538145</v>
+        <v>538057</v>
       </c>
       <c r="R38" t="n">
-        <v>7191409</v>
+        <v>7191361</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4820,7 +4571,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4830,7 +4581,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4857,15 +4608,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>112013918</v>
+        <v>112013871</v>
       </c>
       <c r="B39" t="n">
-        <v>77651</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4873,21 +4619,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4897,10 +4643,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>537989</v>
+        <v>538065</v>
       </c>
       <c r="R39" t="n">
-        <v>7191486</v>
+        <v>7191370</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4932,7 +4678,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4942,7 +4688,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4969,15 +4715,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>112013873</v>
+        <v>112013872</v>
       </c>
       <c r="B40" t="n">
-        <v>78715</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5009,10 +4750,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>538121</v>
+        <v>538123</v>
       </c>
       <c r="R40" t="n">
-        <v>7191384</v>
+        <v>7191380</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -5044,7 +4785,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5054,7 +4795,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5081,15 +4822,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>112013854</v>
+        <v>112013873</v>
       </c>
       <c r="B41" t="n">
-        <v>56446</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5097,38 +4833,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100049</v>
+        <v>2081</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Ryptjärnberget, Ås lm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>537923</v>
+        <v>538121</v>
       </c>
       <c r="R41" t="n">
-        <v>7191446</v>
+        <v>7191384</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -5160,7 +4892,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5170,7 +4902,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5197,15 +4929,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>112013943</v>
+        <v>112013875</v>
       </c>
       <c r="B42" t="n">
-        <v>77651</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5213,21 +4940,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5237,10 +4964,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>538047</v>
+        <v>538139</v>
       </c>
       <c r="R42" t="n">
-        <v>7191331</v>
+        <v>7191426</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -5272,7 +4999,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5282,7 +5009,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5309,37 +5036,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>112013835</v>
+        <v>112013877</v>
       </c>
       <c r="B43" t="n">
-        <v>89518</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5447</v>
+        <v>2081</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5349,10 +5071,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>537612</v>
+        <v>538145</v>
       </c>
       <c r="R43" t="n">
-        <v>7191308</v>
+        <v>7191410</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -5384,7 +5106,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5394,7 +5116,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5421,15 +5143,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>112013939</v>
+        <v>112013878</v>
       </c>
       <c r="B44" t="n">
-        <v>77651</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5437,21 +5154,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5461,10 +5178,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>537977</v>
+        <v>538171</v>
       </c>
       <c r="R44" t="n">
-        <v>7191314</v>
+        <v>7191408</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -5496,7 +5213,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5506,7 +5223,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5533,37 +5250,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>112013863</v>
+        <v>112013839</v>
       </c>
       <c r="B45" t="n">
-        <v>78715</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92632</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>2081</v>
+        <v>3298</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5573,10 +5285,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>537967</v>
+        <v>537982</v>
       </c>
       <c r="R45" t="n">
-        <v>7191330</v>
+        <v>7191483</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5608,7 +5320,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5618,7 +5330,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5645,37 +5357,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>112013947</v>
+        <v>112013834</v>
       </c>
       <c r="B46" t="n">
-        <v>77651</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5685,10 +5392,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>538065</v>
+        <v>537795</v>
       </c>
       <c r="R46" t="n">
-        <v>7191378</v>
+        <v>7191466</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5720,7 +5427,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5730,7 +5437,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5757,37 +5464,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>112013906</v>
+        <v>112013835</v>
       </c>
       <c r="B47" t="n">
-        <v>89568</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1204</v>
+        <v>5447</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5797,10 +5499,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>537811</v>
+        <v>537611</v>
       </c>
       <c r="R47" t="n">
-        <v>7191479</v>
+        <v>7191308</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5832,7 +5534,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5842,7 +5544,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5869,37 +5571,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>112013886</v>
+        <v>112013836</v>
       </c>
       <c r="B48" t="n">
-        <v>78714</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5909,10 +5606,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>538062</v>
+        <v>537709</v>
       </c>
       <c r="R48" t="n">
-        <v>7191346</v>
+        <v>7191221</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -5944,7 +5641,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5954,7 +5651,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5981,54 +5678,45 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>112013841</v>
+        <v>112013837</v>
       </c>
       <c r="B49" t="n">
-        <v>56575</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>103021</v>
+        <v>5447</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Ryptjärnberget, Ås lm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>537897</v>
+        <v>537929</v>
       </c>
       <c r="R49" t="n">
-        <v>7191458</v>
+        <v>7191147</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>
@@ -6060,7 +5748,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6070,7 +5758,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6097,19 +5785,14 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>112013934</v>
+        <v>112013915</v>
       </c>
       <c r="B50" t="n">
-        <v>77651</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
@@ -6137,10 +5820,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>537921</v>
+        <v>538085</v>
       </c>
       <c r="R50" t="n">
-        <v>7191140</v>
+        <v>7191513</v>
       </c>
       <c r="S50" t="n">
         <v>25</v>
@@ -6172,7 +5855,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6182,7 +5865,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6209,37 +5892,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>112013887</v>
+        <v>112013916</v>
       </c>
       <c r="B51" t="n">
-        <v>78714</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6249,10 +5927,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>538057</v>
+        <v>538029</v>
       </c>
       <c r="R51" t="n">
-        <v>7191361</v>
+        <v>7191491</v>
       </c>
       <c r="S51" t="n">
         <v>25</v>
@@ -6284,7 +5962,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6294,7 +5972,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6321,37 +5999,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>112013869</v>
+        <v>112013917</v>
       </c>
       <c r="B52" t="n">
-        <v>78715</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6361,10 +6034,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>538057</v>
+        <v>537995</v>
       </c>
       <c r="R52" t="n">
-        <v>7191361</v>
+        <v>7191487</v>
       </c>
       <c r="S52" t="n">
         <v>25</v>
@@ -6396,7 +6069,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6406,7 +6079,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6433,19 +6106,14 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>112013932</v>
+        <v>112013918</v>
       </c>
       <c r="B53" t="n">
-        <v>77651</v>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
@@ -6473,10 +6141,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>537764</v>
+        <v>537989</v>
       </c>
       <c r="R53" t="n">
-        <v>7191026</v>
+        <v>7191486</v>
       </c>
       <c r="S53" t="n">
         <v>25</v>
@@ -6508,7 +6176,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6518,7 +6186,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6545,19 +6213,14 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>112013942</v>
+        <v>112013919</v>
       </c>
       <c r="B54" t="n">
-        <v>77651</v>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
@@ -6585,10 +6248,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>538057</v>
+        <v>537973</v>
       </c>
       <c r="R54" t="n">
-        <v>7191309</v>
+        <v>7191498</v>
       </c>
       <c r="S54" t="n">
         <v>25</v>
@@ -6620,7 +6283,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6630,7 +6293,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6657,37 +6320,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>112013837</v>
+        <v>112013920</v>
       </c>
       <c r="B55" t="n">
-        <v>89518</v>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6697,10 +6355,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>537929</v>
+        <v>537932</v>
       </c>
       <c r="R55" t="n">
-        <v>7191147</v>
+        <v>7191471</v>
       </c>
       <c r="S55" t="n">
         <v>25</v>
@@ -6732,7 +6390,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6742,7 +6400,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6769,37 +6427,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>112013908</v>
+        <v>112013921</v>
       </c>
       <c r="B56" t="n">
-        <v>89568</v>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6809,10 +6462,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>537709</v>
+        <v>537878</v>
       </c>
       <c r="R56" t="n">
-        <v>7191221</v>
+        <v>7191453</v>
       </c>
       <c r="S56" t="n">
         <v>25</v>
@@ -6844,7 +6497,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6854,7 +6507,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6881,37 +6534,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>112013888</v>
+        <v>112013922</v>
       </c>
       <c r="B57" t="n">
-        <v>78714</v>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6921,10 +6569,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>538066</v>
+        <v>537814</v>
       </c>
       <c r="R57" t="n">
-        <v>7191370</v>
+        <v>7191480</v>
       </c>
       <c r="S57" t="n">
         <v>25</v>
@@ -6956,7 +6604,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6966,7 +6614,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6993,19 +6641,14 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>112013946</v>
+        <v>112013923</v>
       </c>
       <c r="B58" t="n">
-        <v>77651</v>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
@@ -7033,10 +6676,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>538066</v>
+        <v>537799</v>
       </c>
       <c r="R58" t="n">
-        <v>7191370</v>
+        <v>7191449</v>
       </c>
       <c r="S58" t="n">
         <v>25</v>
@@ -7068,7 +6711,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7078,7 +6721,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7105,37 +6748,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>112013911</v>
+        <v>112013924</v>
       </c>
       <c r="B59" t="n">
-        <v>89568</v>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7145,10 +6783,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>538047</v>
+        <v>537753</v>
       </c>
       <c r="R59" t="n">
-        <v>7191331</v>
+        <v>7191465</v>
       </c>
       <c r="S59" t="n">
         <v>25</v>
@@ -7180,7 +6818,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7190,7 +6828,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7217,19 +6855,14 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>112013938</v>
+        <v>112013925</v>
       </c>
       <c r="B60" t="n">
-        <v>77651</v>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
@@ -7257,10 +6890,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>537931</v>
+        <v>537658</v>
       </c>
       <c r="R60" t="n">
-        <v>7191312</v>
+        <v>7191464</v>
       </c>
       <c r="S60" t="n">
         <v>25</v>
@@ -7292,7 +6925,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7302,7 +6935,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7329,54 +6962,45 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>112013842</v>
+        <v>112013926</v>
       </c>
       <c r="B61" t="n">
-        <v>56575</v>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Ryptjärnberget, Ås lm</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>537654</v>
+        <v>537626</v>
       </c>
       <c r="R61" t="n">
-        <v>7191445</v>
+        <v>7191353</v>
       </c>
       <c r="S61" t="n">
         <v>25</v>
@@ -7408,7 +7032,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7418,7 +7042,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7445,37 +7069,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>112013894</v>
+        <v>112013927</v>
       </c>
       <c r="B62" t="n">
-        <v>78748</v>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7485,10 +7104,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>538062</v>
+        <v>537611</v>
       </c>
       <c r="R62" t="n">
-        <v>7191381</v>
+        <v>7191308</v>
       </c>
       <c r="S62" t="n">
         <v>25</v>
@@ -7520,7 +7139,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7530,7 +7149,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7557,37 +7176,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>112013955</v>
+        <v>112013928</v>
       </c>
       <c r="B63" t="n">
-        <v>85851</v>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A. Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7597,10 +7211,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>537931</v>
+        <v>537705</v>
       </c>
       <c r="R63" t="n">
-        <v>7191154</v>
+        <v>7191217</v>
       </c>
       <c r="S63" t="n">
         <v>25</v>
@@ -7632,7 +7246,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7642,7 +7256,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7669,37 +7283,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>112013893</v>
+        <v>112013929</v>
       </c>
       <c r="B64" t="n">
-        <v>78748</v>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7709,10 +7318,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>538060</v>
+        <v>537696</v>
       </c>
       <c r="R64" t="n">
-        <v>7191364</v>
+        <v>7191132</v>
       </c>
       <c r="S64" t="n">
         <v>25</v>
@@ -7744,7 +7353,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7754,7 +7363,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7781,37 +7390,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>112013954</v>
+        <v>112013930</v>
       </c>
       <c r="B65" t="n">
-        <v>81386</v>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7821,10 +7425,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>537931</v>
+        <v>537702</v>
       </c>
       <c r="R65" t="n">
-        <v>7191309</v>
+        <v>7191092</v>
       </c>
       <c r="S65" t="n">
         <v>25</v>
@@ -7856,7 +7460,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7866,7 +7470,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7893,19 +7497,14 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>112013952</v>
+        <v>112013931</v>
       </c>
       <c r="B66" t="n">
-        <v>77651</v>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
@@ -7933,10 +7532,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>538145</v>
+        <v>537723</v>
       </c>
       <c r="R66" t="n">
-        <v>7191410</v>
+        <v>7191048</v>
       </c>
       <c r="S66" t="n">
         <v>25</v>
@@ -7968,7 +7567,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7978,7 +7577,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8005,37 +7604,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>112013866</v>
+        <v>112013932</v>
       </c>
       <c r="B67" t="n">
-        <v>78715</v>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -8045,10 +7639,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>538054</v>
+        <v>537764</v>
       </c>
       <c r="R67" t="n">
-        <v>7191309</v>
+        <v>7191027</v>
       </c>
       <c r="S67" t="n">
         <v>25</v>
@@ -8080,7 +7674,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8090,7 +7684,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8117,37 +7711,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>112013836</v>
+        <v>112013933</v>
       </c>
       <c r="B68" t="n">
-        <v>89518</v>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -8157,10 +7746,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>537709</v>
+        <v>537762</v>
       </c>
       <c r="R68" t="n">
-        <v>7191221</v>
+        <v>7191031</v>
       </c>
       <c r="S68" t="n">
         <v>25</v>
@@ -8192,7 +7781,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8202,7 +7791,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8229,19 +7818,14 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>112013924</v>
+        <v>112013934</v>
       </c>
       <c r="B69" t="n">
-        <v>77651</v>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
@@ -8269,10 +7853,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>537752</v>
+        <v>537920</v>
       </c>
       <c r="R69" t="n">
-        <v>7191465</v>
+        <v>7191140</v>
       </c>
       <c r="S69" t="n">
         <v>25</v>
@@ -8304,7 +7888,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8314,7 +7898,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8341,37 +7925,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>112013851</v>
+        <v>112013935</v>
       </c>
       <c r="B70" t="n">
-        <v>78741</v>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8381,10 +7960,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>538171</v>
+        <v>537926</v>
       </c>
       <c r="R70" t="n">
-        <v>7191408</v>
+        <v>7191143</v>
       </c>
       <c r="S70" t="n">
         <v>25</v>
@@ -8416,7 +7995,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8426,7 +8005,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8453,37 +8032,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>112013878</v>
+        <v>112013936</v>
       </c>
       <c r="B71" t="n">
-        <v>78715</v>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8493,10 +8067,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>538171</v>
+        <v>537927</v>
       </c>
       <c r="R71" t="n">
-        <v>7191408</v>
+        <v>7191150</v>
       </c>
       <c r="S71" t="n">
         <v>25</v>
@@ -8528,7 +8102,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8538,7 +8112,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8565,37 +8139,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>112013889</v>
+        <v>112013937</v>
       </c>
       <c r="B72" t="n">
-        <v>78714</v>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8605,10 +8174,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>538123</v>
+        <v>537929</v>
       </c>
       <c r="R72" t="n">
-        <v>7191380</v>
+        <v>7191155</v>
       </c>
       <c r="S72" t="n">
         <v>25</v>
@@ -8640,7 +8209,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8650,7 +8219,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8677,37 +8246,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>112013907</v>
+        <v>112013938</v>
       </c>
       <c r="B73" t="n">
-        <v>89568</v>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8717,10 +8281,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>537752</v>
+        <v>537931</v>
       </c>
       <c r="R73" t="n">
-        <v>7191465</v>
+        <v>7191311</v>
       </c>
       <c r="S73" t="n">
         <v>25</v>
@@ -8752,7 +8316,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8762,7 +8326,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8789,19 +8353,14 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>112013951</v>
+        <v>112013939</v>
       </c>
       <c r="B74" t="n">
-        <v>77651</v>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
@@ -8829,10 +8388,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>538140</v>
+        <v>537977</v>
       </c>
       <c r="R74" t="n">
-        <v>7191413</v>
+        <v>7191314</v>
       </c>
       <c r="S74" t="n">
         <v>25</v>
@@ -8864,7 +8423,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8874,7 +8433,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8901,37 +8460,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>112013882</v>
+        <v>112013940</v>
       </c>
       <c r="B75" t="n">
-        <v>78714</v>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8941,10 +8495,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>538053</v>
+        <v>538023</v>
       </c>
       <c r="R75" t="n">
-        <v>7191265</v>
+        <v>7191282</v>
       </c>
       <c r="S75" t="n">
         <v>25</v>
@@ -8976,7 +8530,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8986,7 +8540,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9013,37 +8567,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>112013867</v>
+        <v>112013941</v>
       </c>
       <c r="B76" t="n">
-        <v>78715</v>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -9053,10 +8602,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>538051</v>
+        <v>538055</v>
       </c>
       <c r="R76" t="n">
-        <v>7191344</v>
+        <v>7191262</v>
       </c>
       <c r="S76" t="n">
         <v>25</v>
@@ -9088,7 +8637,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9098,7 +8647,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9125,37 +8674,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>112013848</v>
+        <v>112013942</v>
       </c>
       <c r="B77" t="n">
-        <v>78741</v>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -9165,10 +8709,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>538062</v>
+        <v>538057</v>
       </c>
       <c r="R77" t="n">
-        <v>7191381</v>
+        <v>7191309</v>
       </c>
       <c r="S77" t="n">
         <v>25</v>
@@ -9200,7 +8744,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9210,7 +8754,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9237,37 +8781,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>112013834</v>
+        <v>112013943</v>
       </c>
       <c r="B78" t="n">
-        <v>89518</v>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -9277,10 +8816,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>537795</v>
+        <v>538047</v>
       </c>
       <c r="R78" t="n">
-        <v>7191466</v>
+        <v>7191331</v>
       </c>
       <c r="S78" t="n">
         <v>25</v>
@@ -9312,7 +8851,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9322,7 +8861,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9349,19 +8888,14 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>112013941</v>
+        <v>112013944</v>
       </c>
       <c r="B79" t="n">
-        <v>77651</v>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
@@ -9389,10 +8923,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>538055</v>
+        <v>538049</v>
       </c>
       <c r="R79" t="n">
-        <v>7191262</v>
+        <v>7191349</v>
       </c>
       <c r="S79" t="n">
         <v>25</v>
@@ -9424,7 +8958,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9434,7 +8968,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9461,37 +8995,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>112013913</v>
+        <v>112013945</v>
       </c>
       <c r="B80" t="n">
-        <v>89568</v>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9501,10 +9030,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>538065</v>
+        <v>538062</v>
       </c>
       <c r="R80" t="n">
-        <v>7191378</v>
+        <v>7191368</v>
       </c>
       <c r="S80" t="n">
         <v>25</v>
@@ -9536,7 +9065,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9546,7 +9075,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9573,19 +9102,14 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>112013926</v>
+        <v>112013946</v>
       </c>
       <c r="B81" t="n">
-        <v>77651</v>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E81" t="n">
@@ -9613,10 +9137,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>537626</v>
+        <v>538065</v>
       </c>
       <c r="R81" t="n">
-        <v>7191352</v>
+        <v>7191370</v>
       </c>
       <c r="S81" t="n">
         <v>25</v>
@@ -9648,7 +9172,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9658,7 +9182,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9685,37 +9209,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>112013857</v>
+        <v>112013947</v>
       </c>
       <c r="B82" t="n">
-        <v>78715</v>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9725,10 +9244,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>537998</v>
+        <v>538066</v>
       </c>
       <c r="R82" t="n">
-        <v>7191490</v>
+        <v>7191378</v>
       </c>
       <c r="S82" t="n">
         <v>25</v>
@@ -9760,7 +9279,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9770,7 +9289,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9797,37 +9316,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>112013845</v>
+        <v>112013948</v>
       </c>
       <c r="B83" t="n">
-        <v>78741</v>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9837,10 +9351,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>538057</v>
+        <v>538110</v>
       </c>
       <c r="R83" t="n">
-        <v>7191310</v>
+        <v>7191369</v>
       </c>
       <c r="S83" t="n">
         <v>25</v>
@@ -9872,7 +9386,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9882,7 +9396,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9909,37 +9423,32 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>112013877</v>
+        <v>112013949</v>
       </c>
       <c r="B84" t="n">
-        <v>78715</v>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9949,10 +9458,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>538145</v>
+        <v>538123</v>
       </c>
       <c r="R84" t="n">
-        <v>7191410</v>
+        <v>7191383</v>
       </c>
       <c r="S84" t="n">
         <v>25</v>
@@ -9984,7 +9493,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9994,7 +9503,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -10021,37 +9530,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>112013890</v>
+        <v>112013950</v>
       </c>
       <c r="B85" t="n">
-        <v>78714</v>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -10061,10 +9565,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>538121</v>
+        <v>538122</v>
       </c>
       <c r="R85" t="n">
-        <v>7191387</v>
+        <v>7191376</v>
       </c>
       <c r="S85" t="n">
         <v>25</v>
@@ -10133,37 +9637,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>112013852</v>
+        <v>112013951</v>
       </c>
       <c r="B86" t="n">
-        <v>89500</v>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>112</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -10173,10 +9672,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>537929</v>
+        <v>538140</v>
       </c>
       <c r="R86" t="n">
-        <v>7191147</v>
+        <v>7191413</v>
       </c>
       <c r="S86" t="n">
         <v>25</v>
@@ -10208,7 +9707,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -10218,7 +9717,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10245,37 +9744,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>112013846</v>
+        <v>112013952</v>
       </c>
       <c r="B87" t="n">
-        <v>78741</v>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -10285,10 +9779,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>538051</v>
+        <v>538145</v>
       </c>
       <c r="R87" t="n">
-        <v>7191344</v>
+        <v>7191410</v>
       </c>
       <c r="S87" t="n">
         <v>25</v>
@@ -10320,7 +9814,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -10330,7 +9824,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10357,19 +9851,14 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>112013945</v>
+        <v>112013953</v>
       </c>
       <c r="B88" t="n">
-        <v>77651</v>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E88" t="n">
@@ -10397,10 +9886,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>538063</v>
+        <v>538198</v>
       </c>
       <c r="R88" t="n">
-        <v>7191368</v>
+        <v>7191468</v>
       </c>
       <c r="S88" t="n">
         <v>25</v>
@@ -10432,7 +9921,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10442,7 +9931,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10469,15 +9958,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>112013949</v>
+        <v>112013833</v>
       </c>
       <c r="B89" t="n">
-        <v>77651</v>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10485,21 +9969,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -10509,10 +9993,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>538123</v>
+        <v>537972</v>
       </c>
       <c r="R89" t="n">
-        <v>7191383</v>
+        <v>7191315</v>
       </c>
       <c r="S89" t="n">
         <v>25</v>
@@ -10544,7 +10028,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10554,7 +10038,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10581,15 +10065,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>112013883</v>
+        <v>1994518</v>
       </c>
       <c r="B90" t="n">
-        <v>78714</v>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10621,13 +10100,13 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>538038</v>
+        <v>538048</v>
       </c>
       <c r="R90" t="n">
-        <v>7191289</v>
+        <v>7191347</v>
       </c>
       <c r="S90" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -10651,22 +10130,12 @@
       </c>
       <c r="Y90" t="inlineStr">
         <is>
-          <t>2023-09-10</t>
-        </is>
-      </c>
-      <c r="Z90" t="inlineStr">
-        <is>
-          <t>10:22</t>
+          <t>2012-08-26</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2023-09-10</t>
-        </is>
-      </c>
-      <c r="AB90" t="inlineStr">
-        <is>
-          <t>10:22</t>
+          <t>2012-08-26</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10677,53 +10146,53 @@
       </c>
       <c r="AG90" t="b">
         <v>0</v>
+      </c>
+      <c r="AH90" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>SCA Naturvärdesinventeringar</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Via SCA Naturvärdesinventeringar</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>112013892</v>
+        <v>112013881</v>
       </c>
       <c r="B91" t="n">
-        <v>78748</v>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10733,10 +10202,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>537967</v>
+        <v>538023</v>
       </c>
       <c r="R91" t="n">
-        <v>7191330</v>
+        <v>7191282</v>
       </c>
       <c r="S91" t="n">
         <v>25</v>
@@ -10768,7 +10237,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10778,7 +10247,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10805,15 +10274,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>112013899</v>
+        <v>112013882</v>
       </c>
       <c r="B92" t="n">
-        <v>77732</v>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10821,21 +10285,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>864</v>
+        <v>6458</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10845,10 +10309,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>537696</v>
+        <v>538053</v>
       </c>
       <c r="R92" t="n">
-        <v>7191137</v>
+        <v>7191265</v>
       </c>
       <c r="S92" t="n">
         <v>25</v>
@@ -10880,7 +10344,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10890,7 +10354,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10917,15 +10381,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>112013950</v>
+        <v>112013883</v>
       </c>
       <c r="B93" t="n">
-        <v>77651</v>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10933,21 +10392,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10957,10 +10416,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>538123</v>
+        <v>538037</v>
       </c>
       <c r="R93" t="n">
-        <v>7191376</v>
+        <v>7191289</v>
       </c>
       <c r="S93" t="n">
         <v>25</v>
@@ -10992,7 +10451,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -11002,7 +10461,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -11029,15 +10488,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>112013910</v>
+        <v>112013884</v>
       </c>
       <c r="B94" t="n">
-        <v>89568</v>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11045,21 +10499,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>1204</v>
+        <v>6458</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -11069,10 +10523,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>537930</v>
+        <v>538048</v>
       </c>
       <c r="R94" t="n">
-        <v>7191312</v>
+        <v>7191309</v>
       </c>
       <c r="S94" t="n">
         <v>25</v>
@@ -11104,7 +10558,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -11114,7 +10568,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -11141,15 +10595,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>112013944</v>
+        <v>112013886</v>
       </c>
       <c r="B95" t="n">
-        <v>77651</v>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11157,21 +10606,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -11181,10 +10630,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>538049</v>
+        <v>538062</v>
       </c>
       <c r="R95" t="n">
-        <v>7191349</v>
+        <v>7191346</v>
       </c>
       <c r="S95" t="n">
         <v>25</v>
@@ -11216,7 +10665,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -11226,7 +10675,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11253,15 +10702,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>112013861</v>
+        <v>112013887</v>
       </c>
       <c r="B96" t="n">
-        <v>78715</v>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11269,21 +10713,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -11293,10 +10737,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>537931</v>
+        <v>538057</v>
       </c>
       <c r="R96" t="n">
-        <v>7191475</v>
+        <v>7191361</v>
       </c>
       <c r="S96" t="n">
         <v>25</v>
@@ -11328,7 +10772,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -11338,7 +10782,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11365,15 +10809,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>112013853</v>
+        <v>112013888</v>
       </c>
       <c r="B97" t="n">
-        <v>89500</v>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11381,21 +10820,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>112</v>
+        <v>6458</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -11405,10 +10844,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>537930</v>
+        <v>538065</v>
       </c>
       <c r="R97" t="n">
-        <v>7191154</v>
+        <v>7191370</v>
       </c>
       <c r="S97" t="n">
         <v>25</v>
@@ -11440,7 +10879,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -11450,7 +10889,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11477,15 +10916,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>112013871</v>
+        <v>112013889</v>
       </c>
       <c r="B98" t="n">
-        <v>78715</v>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11493,21 +10927,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -11517,10 +10951,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>538066</v>
+        <v>538123</v>
       </c>
       <c r="R98" t="n">
-        <v>7191370</v>
+        <v>7191380</v>
       </c>
       <c r="S98" t="n">
         <v>25</v>
@@ -11552,7 +10986,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -11562,7 +10996,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11589,15 +11023,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>112013917</v>
+        <v>112013890</v>
       </c>
       <c r="B99" t="n">
-        <v>77651</v>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11605,21 +11034,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -11629,10 +11058,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>537995</v>
+        <v>538121</v>
       </c>
       <c r="R99" t="n">
-        <v>7191487</v>
+        <v>7191387</v>
       </c>
       <c r="S99" t="n">
         <v>25</v>
@@ -11664,7 +11093,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -11674,7 +11103,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11701,37 +11130,32 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>112013922</v>
+        <v>112013844</v>
       </c>
       <c r="B100" t="n">
-        <v>77651</v>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11741,10 +11165,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>537814</v>
+        <v>537620</v>
       </c>
       <c r="R100" t="n">
-        <v>7191480</v>
+        <v>7191359</v>
       </c>
       <c r="S100" t="n">
         <v>25</v>
@@ -11776,7 +11200,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -11786,7 +11210,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11813,37 +11237,32 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>112013879</v>
+        <v>112013845</v>
       </c>
       <c r="B101" t="n">
-        <v>89835</v>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>658</v>
+        <v>6462</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11853,10 +11272,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>537709</v>
+        <v>538057</v>
       </c>
       <c r="R101" t="n">
-        <v>7191221</v>
+        <v>7191310</v>
       </c>
       <c r="S101" t="n">
         <v>25</v>
@@ -11888,7 +11307,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -11898,7 +11317,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11925,37 +11344,32 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>112013865</v>
+        <v>112013846</v>
       </c>
       <c r="B102" t="n">
-        <v>78715</v>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11965,10 +11379,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>538032</v>
+        <v>538051</v>
       </c>
       <c r="R102" t="n">
-        <v>7191291</v>
+        <v>7191344</v>
       </c>
       <c r="S102" t="n">
         <v>25</v>
@@ -12000,7 +11414,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -12010,7 +11424,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -12037,37 +11451,32 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>112013860</v>
+        <v>112013847</v>
       </c>
       <c r="B103" t="n">
-        <v>78715</v>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -12077,10 +11486,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>537969</v>
+        <v>538057</v>
       </c>
       <c r="R103" t="n">
-        <v>7191507</v>
+        <v>7191362</v>
       </c>
       <c r="S103" t="n">
         <v>25</v>
@@ -12112,7 +11521,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -12122,7 +11531,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -12149,37 +11558,32 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>112013900</v>
+        <v>112013848</v>
       </c>
       <c r="B104" t="n">
-        <v>77732</v>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>864</v>
+        <v>6462</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -12189,10 +11593,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>537918</v>
+        <v>538061</v>
       </c>
       <c r="R104" t="n">
-        <v>7191139</v>
+        <v>7191381</v>
       </c>
       <c r="S104" t="n">
         <v>25</v>
@@ -12224,7 +11628,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -12234,7 +11638,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -12261,15 +11665,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>112013844</v>
+        <v>112013849</v>
       </c>
       <c r="B105" t="n">
-        <v>78741</v>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12301,10 +11700,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>537620</v>
+        <v>538138</v>
       </c>
       <c r="R105" t="n">
-        <v>7191360</v>
+        <v>7191417</v>
       </c>
       <c r="S105" t="n">
         <v>25</v>
@@ -12336,7 +11735,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -12346,7 +11745,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -12373,37 +11772,32 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>112013855</v>
+        <v>112013850</v>
       </c>
       <c r="B106" t="n">
-        <v>73833</v>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6486</v>
+        <v>6462</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -12413,10 +11807,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>538040</v>
+        <v>538145</v>
       </c>
       <c r="R106" t="n">
-        <v>7191335</v>
+        <v>7191409</v>
       </c>
       <c r="S106" t="n">
         <v>25</v>
@@ -12448,7 +11842,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -12458,7 +11852,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12485,37 +11879,32 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>112013933</v>
+        <v>112013851</v>
       </c>
       <c r="B107" t="n">
-        <v>77651</v>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -12525,10 +11914,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>537762</v>
+        <v>538171</v>
       </c>
       <c r="R107" t="n">
-        <v>7191031</v>
+        <v>7191408</v>
       </c>
       <c r="S107" t="n">
         <v>25</v>
@@ -12560,7 +11949,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -12570,7 +11959,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12597,37 +11986,32 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>112013940</v>
+        <v>112013891</v>
       </c>
       <c r="B108" t="n">
-        <v>77651</v>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80468</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -12637,10 +12021,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>538024</v>
+        <v>538029</v>
       </c>
       <c r="R108" t="n">
-        <v>7191282</v>
+        <v>7191489</v>
       </c>
       <c r="S108" t="n">
         <v>25</v>
@@ -12672,7 +12056,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -12682,7 +12066,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12709,37 +12093,32 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>112013859</v>
+        <v>112013892</v>
       </c>
       <c r="B109" t="n">
-        <v>78715</v>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80468</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>2081</v>
+        <v>6464</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -12749,10 +12128,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>537984</v>
+        <v>537967</v>
       </c>
       <c r="R109" t="n">
-        <v>7191480</v>
+        <v>7191330</v>
       </c>
       <c r="S109" t="n">
         <v>25</v>
@@ -12784,7 +12163,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -12794,7 +12173,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12821,37 +12200,32 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>112013927</v>
+        <v>112013893</v>
       </c>
       <c r="B110" t="n">
-        <v>77651</v>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80468</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -12861,10 +12235,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>537612</v>
+        <v>538059</v>
       </c>
       <c r="R110" t="n">
-        <v>7191308</v>
+        <v>7191364</v>
       </c>
       <c r="S110" t="n">
         <v>25</v>
@@ -12896,7 +12270,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -12906,7 +12280,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12933,55 +12307,45 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>112013840</v>
+        <v>112013894</v>
       </c>
       <c r="B111" t="n">
-        <v>56430</v>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80468</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
-      <c r="M111" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P111" t="inlineStr">
         <is>
           <t>Ryptjärnberget, Ås lm</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>537631</v>
+        <v>538061</v>
       </c>
       <c r="R111" t="n">
-        <v>7191461</v>
+        <v>7191381</v>
       </c>
       <c r="S111" t="n">
         <v>25</v>
@@ -13013,7 +12377,7 @@
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
@@ -13023,7 +12387,7 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -13050,15 +12414,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>112013849</v>
+        <v>112013895</v>
       </c>
       <c r="B112" t="n">
-        <v>78741</v>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80468</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13066,21 +12425,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6462</v>
+        <v>6464</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -13090,10 +12449,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>538138</v>
+        <v>538123</v>
       </c>
       <c r="R112" t="n">
-        <v>7191417</v>
+        <v>7191387</v>
       </c>
       <c r="S112" t="n">
         <v>25</v>
@@ -13125,7 +12484,7 @@
       </c>
       <c r="Z112" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
@@ -13135,7 +12494,7 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -13162,37 +12521,32 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>112013936</v>
+        <v>112013855</v>
       </c>
       <c r="B113" t="n">
-        <v>77651</v>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83305</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6425</v>
+        <v>6486</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -13202,10 +12556,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>537926</v>
+        <v>538040</v>
       </c>
       <c r="R113" t="n">
-        <v>7191150</v>
+        <v>7191335</v>
       </c>
       <c r="S113" t="n">
         <v>25</v>
@@ -13237,7 +12591,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -13247,7 +12601,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -13274,50 +12628,49 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>112013919</v>
+        <v>112013854</v>
       </c>
       <c r="B114" t="n">
-        <v>77651</v>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I114" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P114" t="inlineStr">
         <is>
           <t>Ryptjärnberget, Ås lm</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>537973</v>
+        <v>537923</v>
       </c>
       <c r="R114" t="n">
-        <v>7191498</v>
+        <v>7191446</v>
       </c>
       <c r="S114" t="n">
         <v>25</v>
@@ -13349,7 +12702,7 @@
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
@@ -13359,7 +12712,7 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -13386,15 +12739,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>112013928</v>
+        <v>112013840</v>
       </c>
       <c r="B115" t="n">
-        <v>77651</v>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13402,34 +12750,39 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P115" t="inlineStr">
         <is>
           <t>Ryptjärnberget, Ås lm</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>537704</v>
+        <v>537632</v>
       </c>
       <c r="R115" t="n">
-        <v>7191218</v>
+        <v>7191462</v>
       </c>
       <c r="S115" t="n">
         <v>25</v>
@@ -13461,7 +12814,7 @@
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
@@ -13471,7 +12824,7 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -13498,50 +12851,54 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>112013915</v>
+        <v>112013880</v>
       </c>
       <c r="B116" t="n">
-        <v>77651</v>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57144</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6425</v>
+        <v>102613</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I116" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L116" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="P116" t="inlineStr">
         <is>
           <t>Ryptjärnberget, Ås lm</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>538085</v>
+        <v>537602</v>
       </c>
       <c r="R116" t="n">
-        <v>7191513</v>
+        <v>7191352</v>
       </c>
       <c r="S116" t="n">
         <v>25</v>
@@ -13573,7 +12930,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -13583,7 +12940,7 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -13610,15 +12967,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>112013948</v>
+        <v>112013841</v>
       </c>
       <c r="B117" t="n">
-        <v>77651</v>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13626,34 +12978,38 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I117" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P117" t="inlineStr">
         <is>
           <t>Ryptjärnberget, Ås lm</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>538109</v>
+        <v>537898</v>
       </c>
       <c r="R117" t="n">
-        <v>7191369</v>
+        <v>7191458</v>
       </c>
       <c r="S117" t="n">
         <v>25</v>
@@ -13685,7 +13041,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -13695,7 +13051,7 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -13722,15 +13078,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>112013902</v>
+        <v>112013842</v>
       </c>
       <c r="B118" t="n">
-        <v>89550</v>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13738,34 +13089,38 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>1108</v>
+        <v>103021</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I118" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P118" t="inlineStr">
         <is>
           <t>Ryptjärnberget, Ås lm</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>538112</v>
+        <v>537654</v>
       </c>
       <c r="R118" t="n">
-        <v>7191368</v>
+        <v>7191445</v>
       </c>
       <c r="S118" t="n">
         <v>25</v>
@@ -13797,7 +13152,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -13807,7 +13162,7 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13831,6 +13186,438 @@
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>112013898</v>
+      </c>
+      <c r="B119" t="n">
+        <v>58116</v>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E119" t="n">
+        <v>103022</v>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>Lappmes</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>Poecile cinctus</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>(Boddaert, 1783)</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P119" t="inlineStr">
+        <is>
+          <t>Ryptjärnberget, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q119" t="n">
+        <v>537891</v>
+      </c>
+      <c r="R119" t="n">
+        <v>7191464</v>
+      </c>
+      <c r="S119" t="n">
+        <v>25</v>
+      </c>
+      <c r="T119" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U119" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V119" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W119" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y119" t="inlineStr">
+        <is>
+          <t>2023-09-10</t>
+        </is>
+      </c>
+      <c r="Z119" t="inlineStr">
+        <is>
+          <t>12:50</t>
+        </is>
+      </c>
+      <c r="AA119" t="inlineStr">
+        <is>
+          <t>2023-09-10</t>
+        </is>
+      </c>
+      <c r="AB119" t="inlineStr">
+        <is>
+          <t>12:50</t>
+        </is>
+      </c>
+      <c r="AD119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT119" t="inlineStr"/>
+      <c r="AW119" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX119" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY119" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>112013830</v>
+      </c>
+      <c r="B120" t="n">
+        <v>106229</v>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E120" t="n">
+        <v>221725</v>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>Ögonpyrola</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>Moneses uniflora</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr"/>
+      <c r="P120" t="inlineStr">
+        <is>
+          <t>Ryptjärnberget, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q120" t="n">
+        <v>538171</v>
+      </c>
+      <c r="R120" t="n">
+        <v>7191412</v>
+      </c>
+      <c r="S120" t="n">
+        <v>25</v>
+      </c>
+      <c r="T120" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U120" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V120" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W120" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y120" t="inlineStr">
+        <is>
+          <t>2023-09-10</t>
+        </is>
+      </c>
+      <c r="Z120" t="inlineStr">
+        <is>
+          <t>09:43</t>
+        </is>
+      </c>
+      <c r="AA120" t="inlineStr">
+        <is>
+          <t>2023-09-10</t>
+        </is>
+      </c>
+      <c r="AB120" t="inlineStr">
+        <is>
+          <t>09:43</t>
+        </is>
+      </c>
+      <c r="AD120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT120" t="inlineStr"/>
+      <c r="AW120" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX120" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY120" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>112013838</v>
+      </c>
+      <c r="B121" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E121" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr"/>
+      <c r="P121" t="inlineStr">
+        <is>
+          <t>Ryptjärnberget, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q121" t="n">
+        <v>537889</v>
+      </c>
+      <c r="R121" t="n">
+        <v>7191123</v>
+      </c>
+      <c r="S121" t="n">
+        <v>25</v>
+      </c>
+      <c r="T121" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U121" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V121" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W121" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y121" t="inlineStr">
+        <is>
+          <t>2023-09-10</t>
+        </is>
+      </c>
+      <c r="Z121" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="AA121" t="inlineStr">
+        <is>
+          <t>2023-09-10</t>
+        </is>
+      </c>
+      <c r="AB121" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="AD121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT121" t="inlineStr"/>
+      <c r="AW121" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX121" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY121" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>112013897</v>
+      </c>
+      <c r="B122" t="n">
+        <v>92329</v>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E122" t="n">
+        <v>6040186</v>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>Kötticka</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>Leptoporus mollis</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>(Pers.:Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr"/>
+      <c r="P122" t="inlineStr">
+        <is>
+          <t>Ryptjärnberget, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q122" t="n">
+        <v>537927</v>
+      </c>
+      <c r="R122" t="n">
+        <v>7191144</v>
+      </c>
+      <c r="S122" t="n">
+        <v>25</v>
+      </c>
+      <c r="T122" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U122" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V122" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W122" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y122" t="inlineStr">
+        <is>
+          <t>2023-09-10</t>
+        </is>
+      </c>
+      <c r="Z122" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="AA122" t="inlineStr">
+        <is>
+          <t>2023-09-10</t>
+        </is>
+      </c>
+      <c r="AB122" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="AD122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT122" t="inlineStr"/>
+      <c r="AW122" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX122" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY122" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
